--- a/artfynd/A 40866-2023 artfynd.xlsx
+++ b/artfynd/A 40866-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40866-2023 artfynd.xlsx
+++ b/artfynd/A 40866-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -928,125 +928,6 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>116648781</v>
-      </c>
-      <c r="B4" t="n">
-        <v>103269</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>222412</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tibast</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Daphne mezereum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Bodvill 331, Sollefteå, Ång</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>607819</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7022767</v>
-      </c>
-      <c r="S4" t="n">
-        <v>25</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Resele</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2024-05-06</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2024-05-06</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Gunilla Viksten</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Gunilla Viksten</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40866-2023 artfynd.xlsx
+++ b/artfynd/A 40866-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -928,6 +928,112 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125893444</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bodvill , Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>607877</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7022729</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40866-2023 artfynd.xlsx
+++ b/artfynd/A 40866-2023 artfynd.xlsx
@@ -933,7 +933,7 @@
         <v>125893444</v>
       </c>
       <c r="B4" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40866-2023 artfynd.xlsx
+++ b/artfynd/A 40866-2023 artfynd.xlsx
@@ -933,7 +933,7 @@
         <v>125893444</v>
       </c>
       <c r="B4" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40866-2023 artfynd.xlsx
+++ b/artfynd/A 40866-2023 artfynd.xlsx
@@ -933,7 +933,7 @@
         <v>125893444</v>
       </c>
       <c r="B4" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40866-2023 artfynd.xlsx
+++ b/artfynd/A 40866-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>92500199</v>
+        <v>131596052</v>
       </c>
       <c r="B2" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>100038</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,28 +708,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>knoppbristning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bodvill 331, Sollefteå, Ång</t>
+          <t>Bodvill 332, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607819.2208463589</v>
+        <v>607821</v>
       </c>
       <c r="R2" t="n">
-        <v>7022767.284273741</v>
+        <v>7022807</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -761,22 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-04-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-04-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +763,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -804,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111464530</v>
+        <v>115527939</v>
       </c>
       <c r="B3" t="n">
-        <v>55652</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56925</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,48 +792,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208255</v>
+        <v>100045</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>vilande</t>
-        </is>
-      </c>
+          <t>sträckande NO</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bodvill 331, Sollefteå, Ång</t>
+          <t>Bodvill, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607819.2208463589</v>
+        <v>607883</v>
       </c>
       <c r="R3" t="n">
-        <v>7022767.284273741</v>
+        <v>7022760</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -888,22 +858,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125893444</v>
+        <v>117045281</v>
       </c>
       <c r="B4" t="n">
-        <v>57654</v>
+        <v>57966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,16 +911,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -965,19 +935,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bodvill , Ång</t>
+          <t>Bodvill 332, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607877</v>
+        <v>607821</v>
       </c>
       <c r="R4" t="n">
-        <v>7022729</v>
+        <v>7022807</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1004,12 +974,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,7 +1019,7 @@
         <v>132016923</v>
       </c>
       <c r="B5" t="n">
-        <v>57966</v>
+        <v>57988</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133161258</v>
+        <v>115026161</v>
       </c>
       <c r="B6" t="n">
-        <v>57954</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,21 +1143,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102119</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Göktyta</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Jynx torquilla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1187,19 +1167,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bodvill , Ång</t>
+          <t>Bodvill 332, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607877</v>
+        <v>607821</v>
       </c>
       <c r="R6" t="n">
-        <v>7022729</v>
+        <v>7022807</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1226,22 +1206,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,6 +1245,1459 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125893444</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bodvill , Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>607877</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7022729</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>114590164</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100110</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gråspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picus canus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bodvill 332, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>607821</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7022807</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-02-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-02-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133161258</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57964</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102119</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Göktyta</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Jynx torquilla</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bodvill , Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>607877</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7022729</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133995213</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58231</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102980</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ladusvala</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hirundo rustica</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bodvill 332, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>607821</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7022807</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>110634793</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58388</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bodvill 332, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>607821</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7022807</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-07-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-07-06</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>118276487</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bodvill 332, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>607821</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7022807</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-07-07</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-07-07</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>114589980</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bodvill 332, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>607821</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7022807</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-02-08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-02-08</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>115026424</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bodvill 332, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>607821</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7022807</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>115027125</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bodvill 332, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>607821</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7022807</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>115521394</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bodvill 332, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>607821</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7022807</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>113531937</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bodvill 332, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>607821</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7022807</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>111464530</v>
+      </c>
+      <c r="B18" t="n">
+        <v>56884</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bodvill 331, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>607819</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7022767</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>92500199</v>
+      </c>
+      <c r="B19" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>knoppbristning</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bodvill 331, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>607819</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7022767</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2021-04-17</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2021-04-17</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40866-2023 artfynd.xlsx
+++ b/artfynd/A 40866-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131596052</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115527939</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117045281</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1129,6 +1149,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132016923</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1245,6 +1270,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115026161</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1351,6 +1381,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125893444</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1464,6 +1499,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114590164</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1580,6 +1620,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133161258</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1686,6 +1731,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133995213</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1789,6 +1839,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110634793</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1905,6 +1960,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118276487</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2012,6 +2072,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114589980</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2121,6 +2186,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115026424</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2227,6 +2297,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115027125</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2346,6 +2421,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115521394</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2453,6 +2533,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113531937</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2574,6 +2659,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111464530</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2698,8 +2788,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92500199</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 40866-2023 artfynd.xlsx
+++ b/artfynd/A 40866-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ19"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2429,32 +2429,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113531937</v>
+        <v>135867256</v>
       </c>
       <c r="B17" t="n">
-        <v>58085</v>
+        <v>58095</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>205976</v>
+        <v>205974</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Smalnäbbad nötkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Nucifraga caryocatactes macrorhynchos</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>C.L.Brehm, 1823</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2462,22 +2462,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bodvill 332, Sollefteå, Ång</t>
+          <t>Bodvill 331, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>607821</v>
+        <v>607819</v>
       </c>
       <c r="R17" t="n">
-        <v>7022807</v>
+        <v>7022767</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2504,12 +2503,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2535,16 +2544,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113531937</t>
+          <t>https://artportalen.se/Sighting/135867256</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111464530</v>
+        <v>113531937</v>
       </c>
       <c r="B18" t="n">
-        <v>56884</v>
+        <v>58085</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,21 +2561,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>208255</v>
+        <v>205976</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2574,26 +2583,22 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bodvill 331, Sollefteå, Ång</t>
+          <t>Bodvill 332, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>607819</v>
+        <v>607821</v>
       </c>
       <c r="R18" t="n">
-        <v>7022767</v>
+        <v>7022807</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2620,22 +2625,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:49</t>
+          <t>2023-12-05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>09:49</t>
+          <t>2023-12-05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2661,16 +2656,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111464530</t>
+          <t>https://artportalen.se/Sighting/113531937</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>92500199</v>
+        <v>111464530</v>
       </c>
       <c r="B19" t="n">
-        <v>104628</v>
+        <v>56884</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2678,21 +2673,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222412</v>
+        <v>208255</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2700,18 +2695,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>knoppbristning</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bodvill 331, Sollefteå, Ång</t>
@@ -2748,22 +2741,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-04-17</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-04-17</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2772,7 +2765,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2789,6 +2781,135 @@
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111464530</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>92500199</v>
+      </c>
+      <c r="B20" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>knoppbristning</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Bodvill 331, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>607819</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7022767</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2021-04-17</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2021-04-17</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/92500199</t>
         </is>
@@ -2814,6 +2935,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40866-2023 artfynd.xlsx
+++ b/artfynd/A 40866-2023 artfynd.xlsx
@@ -2432,7 +2432,7 @@
         <v>135867256</v>
       </c>
       <c r="B17" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 40866-2023 artfynd.xlsx
+++ b/artfynd/A 40866-2023 artfynd.xlsx
@@ -2432,7 +2432,7 @@
         <v>135867256</v>
       </c>
       <c r="B17" t="n">
-        <v>58097</v>
+        <v>58098</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 40866-2023 artfynd.xlsx
+++ b/artfynd/A 40866-2023 artfynd.xlsx
@@ -2432,7 +2432,7 @@
         <v>135867256</v>
       </c>
       <c r="B17" t="n">
-        <v>58098</v>
+        <v>58102</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 40866-2023 artfynd.xlsx
+++ b/artfynd/A 40866-2023 artfynd.xlsx
@@ -2432,7 +2432,7 @@
         <v>135867256</v>
       </c>
       <c r="B17" t="n">
-        <v>58102</v>
+        <v>58103</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 40866-2023 artfynd.xlsx
+++ b/artfynd/A 40866-2023 artfynd.xlsx
@@ -2432,7 +2432,7 @@
         <v>135867256</v>
       </c>
       <c r="B17" t="n">
-        <v>58103</v>
+        <v>58108</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 40866-2023 artfynd.xlsx
+++ b/artfynd/A 40866-2023 artfynd.xlsx
@@ -2432,7 +2432,7 @@
         <v>135867256</v>
       </c>
       <c r="B17" t="n">
-        <v>58108</v>
+        <v>58121</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
